--- a/paper/Tables/Compliance.xlsx
+++ b/paper/Tables/Compliance.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5195BEAE-24F4-431A-B01F-127CE50418AA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8508"/>
   </bookViews>
   <sheets>
     <sheet name="Compliance" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="179021" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -141,30 +141,30 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -484,24 +484,24 @@
   <dimension ref="A1:AI7"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.5546875" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
     </row>
-    <row r="3" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15" thickBot="true" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -527,7 +527,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:35" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" ht="15.6" thickTop="true" thickBot="true" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7" t="s">
@@ -567,12 +567,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
       <c r="B5">
-        <v>365</v>
+        <v>321</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
@@ -619,69 +619,72 @@
         <v>56.71</v>
       </c>
       <c r="P5">
-        <v>0.8178913738019169</v>
+        <v>0.84476534296028882</v>
       </c>
       <c r="Q5">
-        <v>0.80727272727272725</v>
+        <v>0.84100418410041844</v>
       </c>
       <c r="R5">
-        <v>0.83132530120481929</v>
+        <v>0.85779816513761464</v>
       </c>
       <c r="S5">
-        <v>0.76170212765957446</v>
+        <v>0.80604982206405695</v>
       </c>
       <c r="T5">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="U5">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="V5">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="W5">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="X5">
-        <v>332</v>
+        <v>293</v>
       </c>
       <c r="Y5">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="Z5">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="AA5">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="AB5">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="AC5">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="AD5">
-        <v>87</v>
+        <v>243</v>
       </c>
       <c r="AE5">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AF5">
-        <v>22</v>
+        <v>303</v>
+      </c>
+      <c r="AG5">
+        <v>18</v>
       </c>
       <c r="AH5">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="AI5">
-        <v>207</v>
+        <v>188</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="C6" s="1">
         <f>ROUND(P6*100,2)</f>
@@ -732,64 +735,67 @@
         <v>52.33</v>
       </c>
       <c r="P6">
-        <v>0.76351351351351349</v>
+        <v>0.77651515151515149</v>
       </c>
       <c r="Q6">
-        <v>0.71691176470588236</v>
+        <v>0.73029045643153523</v>
       </c>
       <c r="R6">
-        <v>0.74180327868852458</v>
+        <v>0.75813953488372088</v>
       </c>
       <c r="S6">
-        <v>0.75902335456475589</v>
+        <v>0.7971781305114638</v>
       </c>
       <c r="T6">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="U6">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="V6">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="W6">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="X6">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="Y6">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="Z6">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="AA6">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="AB6">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="AC6">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="AD6">
-        <v>92</v>
+        <v>232</v>
       </c>
       <c r="AE6">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AF6">
-        <v>36</v>
+        <v>284</v>
+      </c>
+      <c r="AG6">
+        <v>31</v>
       </c>
       <c r="AH6">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="AI6">
-        <v>191</v>
+        <v>176</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>9</v>
       </c>
